--- a/server/test/fixtures/workbook/hand-filled.xlsx
+++ b/server/test/fixtures/workbook/hand-filled.xlsx
@@ -510,7 +510,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
